--- a/data/Networth_Raw_Data.xlsx
+++ b/data/Networth_Raw_Data.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAMPLE-100</t>
+          <t>SAMPLE-200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SAMPLE-101</t>
+          <t>SAMPLE-201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAMPLE-102</t>
+          <t>SAMPLE-202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2019-09-17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -615,46 +615,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>100000</v>
+        <v>72029</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>100000</v>
+        <v>72029</v>
       </c>
       <c r="I4" t="n">
-        <v>119000</v>
+        <v>77097</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SAMPLE-103</t>
+          <t>SAMPLE-203</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Member B</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -663,46 +663,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>200000</v>
+        <v>54960</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>200000</v>
+        <v>54960</v>
       </c>
       <c r="I5" t="n">
-        <v>240000</v>
+        <v>58817</v>
       </c>
       <c r="J5" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SAMPLE-104</t>
+          <t>SAMPLE-204</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Member B</t>
+          <t>Member D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2022-03-10</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2027-03-10</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -711,46 +711,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="I6" t="n">
-        <v>195000</v>
+        <v>215072</v>
       </c>
       <c r="J6" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAMPLE-105</t>
+          <t>SAMPLE-205</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Member C</t>
+          <t>Member D</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2027-04-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="I7" t="n">
-        <v>98000</v>
+        <v>347384</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAMPLE-106</t>
+          <t>SAMPLE-206</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -807,25 +807,793 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50000</v>
+        <v>77621</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>50000</v>
+        <v>77621</v>
       </c>
       <c r="I8" t="n">
-        <v>65000</v>
+        <v>83532</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SAMPLE-207</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2028-01-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>7467.76</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7467.76</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8199.139999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SAMPLE-208</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>7324.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7324.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7695.38</v>
+      </c>
+      <c r="J10" t="n">
         <v>5</v>
       </c>
-      <c r="L8" t="n">
-        <v>60</v>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SAMPLE-209</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>7695.16</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7695.16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>9281.24</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SAMPLE-210</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>9530.309999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9530.309999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10589.52</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SAMPLE-211</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>6732.37</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6732.37</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7480.61</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SAMPLE-212</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>11600.12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11600.12</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12325.1275</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SAMPLE-213</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2028-05-05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>7537.41</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7537.41</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8203.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SAMPLE-214</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>7725.96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7725.96</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8094.12</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SAMPLE-215</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2027-04-22</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>7828.35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7929.77</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8177.58</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SAMPLE-216</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2027-04-21</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>422022</v>
+      </c>
+      <c r="G18" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>451714</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SAMPLE-217</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2027-10-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2342229</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2342229</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2863124</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SAMPLE-218</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2029-07-08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>7690.81</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7690.81</v>
+      </c>
+      <c r="I20" t="n">
+        <v>9005.41</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SAMPLE-219</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8442.809999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SAMPLE-220</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8442.809999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SAMPLE-221</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8442.809999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SAMPLE-222</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8442.809999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/data/Networth_Raw_Data.xlsx
+++ b/data/Networth_Raw_Data.xlsx
@@ -2651,7 +2651,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INE092T01019</t>
+          <t>IDFC First Bank</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INE918I01026</t>
+          <t>Bajaj Finserv</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INE296A01032</t>
+          <t>Bajaj Finance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INE263A01024</t>
+          <t>Bharat Electronics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INE153T01027</t>
+          <t>BLS International</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INE216A01030</t>
+          <t>Britannia Industries</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INE259A01022</t>
+          <t>Colgate-Palmolive (India)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INE758T01015</t>
+          <t>Eternal Limited</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INE040A01034</t>
+          <t>HDFC Bank</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INE795G01014</t>
+          <t>HDFC Life Insurance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INE031A01017</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INE758E01017</t>
+          <t>Jio Financial Services</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INE2KCE01013</t>
+          <t>KWIL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INE0FS801015</t>
+          <t>Motherson Sumi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INE663F01032</t>
+          <t>Info Edge (India)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INE589A01014</t>
+          <t>NLC India</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INE160A01022</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INE891D01026</t>
+          <t>Redington</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INE062A01020</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INE040H01021</t>
+          <t>Suzlon Energy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INE245A01021</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INE1TAE01010</t>
+          <t>Tata Motors CV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INE155A01022</t>
+          <t>Tata Motors PV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INE1CDF01017</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INE205A01025</t>
+          <t>Vedanta</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INE694L01019</t>
+          <t>Vedanta Power</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INE1CLE01013</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INE704J01044</t>
+          <t>VOGL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INE192B01031</t>
+          <t>Welspun Living</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INE914E01040</t>
+          <t>Alankit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INE397D01024</t>
+          <t>Bharti Airtel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INE758E01017</t>
+          <t>Jio Financial Services</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN0020230093</t>
+          <t>Sovereign Gold Bond Sep 2031 II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IN0020200427</t>
+          <t>Sovereign Gold Bond Mar 2029 XII</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INF204KB17I5</t>
+          <t>Nippon India ETF Gold BeES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">

--- a/data/Networth_Raw_Data.xlsx
+++ b/data/Networth_Raw_Data.xlsx
@@ -10,7 +10,6 @@
     <sheet name="FD" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="MF" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash in Hand" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,12 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,23 +481,37 @@
           <t>ROI % p.a.</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor Years</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tenor Months</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABC123</t>
+          <t>SAMPLE-200</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>45959</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>46403</v>
+          <t>Member A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2027-01-16</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -524,23 +533,33 @@
       <c r="J2" t="n">
         <v>6.6</v>
       </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABC124</t>
+          <t>SAMPLE-201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>42725</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>47108</v>
+          <t>Member A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2016-12-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2028-12-21</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -562,23 +581,33 @@
       <c r="J3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ABC126</t>
+          <t>SAMPLE-202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>43725</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>46388</v>
+          <t>Member A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2019-09-17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -600,23 +629,33 @@
       <c r="J4" t="n">
         <v>6.25</v>
       </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABC128</t>
+          <t>SAMPLE-203</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>45215</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>46412</v>
+          <t>Member A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2027-01-25</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -638,23 +677,33 @@
       <c r="J5" t="n">
         <v>6.25</v>
       </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABC130</t>
+          <t>SAMPLE-204</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mr. SATYANARAYAN SHARMA</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>45937</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>46333</v>
+          <t>Member D</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-11-07</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -676,23 +725,33 @@
       <c r="J6" t="n">
         <v>6.75</v>
       </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABC132</t>
+          <t>SAMPLE-205</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mr. SATYANARAYAN SHARMA</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>45771</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>46501</v>
+          <t>Member D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2027-04-24</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -714,61 +773,81 @@
       <c r="J7" t="n">
         <v>7.4</v>
       </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABC136</t>
+          <t>SAMPLE-206</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>46035</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>46759</v>
+          <t>Member D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7467.76</v>
+        <v>77621</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>7467.76</v>
+        <v>77621</v>
       </c>
       <c r="I8" t="n">
-        <v>8199.139999999999</v>
+        <v>83532</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>6.75</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABC138</t>
+          <t>SAMPLE-207</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>46309</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>46674</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2028-01-07</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -776,37 +855,47 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7692.33</v>
+        <v>7467.76</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7692.33</v>
+        <v>7467.76</v>
       </c>
       <c r="I9" t="n">
-        <v>8035.49</v>
+        <v>8199.139999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABC140</t>
+          <t>SAMPLE-208</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>46260</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>47356</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -814,37 +903,47 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7695.16</v>
+        <v>7324.09</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7695.16</v>
+        <v>7324.09</v>
       </c>
       <c r="I10" t="n">
-        <v>9281.24</v>
+        <v>7695.38</v>
       </c>
       <c r="J10" t="n">
-        <v>6.25</v>
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABC142</t>
+          <t>SAMPLE-209</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>46454</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2029-08-26</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -852,37 +951,47 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9530.309999999999</v>
+        <v>7695.16</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>9530.309999999999</v>
+        <v>7695.16</v>
       </c>
       <c r="I11" t="n">
-        <v>10589.52</v>
+        <v>9281.24</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABC144</t>
+          <t>SAMPLE-210</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>45672</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>46371</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -890,37 +999,47 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6732.37</v>
+        <v>9530.309999999999</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>6732.37</v>
+        <v>9530.309999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>7480.61</v>
+        <v>10589.52</v>
       </c>
       <c r="J12" t="n">
         <v>5.5</v>
       </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABC146</t>
+          <t>SAMPLE-211</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>46289</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>46654</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-12-15</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -928,37 +1047,47 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11595.12</v>
+        <v>6732.37</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>11595.12</v>
+        <v>6732.37</v>
       </c>
       <c r="I13" t="n">
-        <v>12046.27</v>
+        <v>7480.61</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ABC148</t>
+          <t>SAMPLE-212</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>45478</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>46878</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2029-09-01</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -966,37 +1095,47 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7537.41</v>
+        <v>11600.12</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7537.41</v>
+        <v>11600.12</v>
       </c>
       <c r="I14" t="n">
-        <v>8203.25</v>
+        <v>12325.1275</v>
       </c>
       <c r="J14" t="n">
-        <v>5.65</v>
+        <v>6.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABC150</t>
+          <t>SAMPLE-213</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>45300</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>46396</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2028-05-05</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1004,37 +1143,47 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7725.96</v>
+        <v>7537.41</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>7725.96</v>
+        <v>7537.41</v>
       </c>
       <c r="I15" t="n">
-        <v>8094.12</v>
+        <v>8203.25</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>5.65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABC152</t>
+          <t>SAMPLE-214</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>46134</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>46499</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2027-01-09</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1042,75 +1191,95 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7828.35</v>
+        <v>7725.96</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>7929.77</v>
+        <v>7725.96</v>
       </c>
       <c r="I16" t="n">
-        <v>8177.58</v>
+        <v>8094.12</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABC154</t>
+          <t>SAMPLE-215</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>45698</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>46498</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2027-04-22</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>422022</v>
+        <v>7828.35</v>
       </c>
       <c r="G17" t="n">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>7929.77</v>
       </c>
       <c r="I17" t="n">
-        <v>451714</v>
+        <v>8177.58</v>
       </c>
       <c r="J17" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ABC156</t>
+          <t>SAMPLE-216</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>44495</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>46686</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2027-04-21</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1118,75 +1287,95 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2342229</v>
+        <v>422022</v>
       </c>
       <c r="G18" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="n">
-        <v>2342229</v>
-      </c>
       <c r="I18" t="n">
-        <v>2863124</v>
+        <v>451714</v>
       </c>
       <c r="J18" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ABC158</t>
+          <t>SAMPLE-217</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>46211</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>47307</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2027-10-26</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7690.81</v>
+        <v>2342229</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>7690.81</v>
+        <v>2342229</v>
       </c>
       <c r="I19" t="n">
-        <v>9005.41</v>
+        <v>2863124</v>
       </c>
       <c r="J19" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ABC160</t>
+          <t>SAMPLE-218</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>47331</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2029-07-08</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1194,37 +1383,47 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7000</v>
+        <v>7690.81</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7000</v>
+        <v>7690.81</v>
       </c>
       <c r="I20" t="n">
-        <v>8442.809999999999</v>
+        <v>9005.41</v>
       </c>
       <c r="J20" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ABC162</t>
+          <t>SAMPLE-219</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>47331</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1246,23 +1445,33 @@
       <c r="J21" t="n">
         <v>6.25</v>
       </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ABC164</t>
+          <t>SAMPLE-220</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>47331</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1284,23 +1493,33 @@
       <c r="J22" t="n">
         <v>6.25</v>
       </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ABC166</t>
+          <t>SAMPLE-221</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>46235</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>47331</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1322,81 +1541,59 @@
       <c r="J23" t="n">
         <v>6.25</v>
       </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ABC168</t>
+          <t>SAMPLE-222</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>46307</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>46751</v>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2029-08-01</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1200000</v>
+        <v>7000</v>
       </c>
       <c r="I24" t="n">
-        <v>1297152</v>
+        <v>8442.809999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ABC170</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>46307</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>46672</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>7800.99</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>7800.99</v>
-      </c>
-      <c r="I25" t="n">
-        <v>8068.26</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.35</v>
+        <v>6.25</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1410,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,7 +1660,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -1500,7 +1697,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -1537,7 +1734,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -1574,7 +1771,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1611,7 +1808,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -1648,7 +1845,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -1685,7 +1882,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1722,7 +1919,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1759,7 +1956,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1796,7 +1993,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1816,13 +2013,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>21052.956</v>
+        <v>16331.145</v>
       </c>
       <c r="G11" t="n">
-        <v>28.37</v>
+        <v>28.49</v>
       </c>
       <c r="H11" t="n">
-        <v>597272.3617199999</v>
+        <v>465274.32105</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1833,7 +2030,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1853,13 +2050,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5435.758</v>
+        <v>4392.465</v>
       </c>
       <c r="G12" t="n">
-        <v>126.91</v>
+        <v>127.32</v>
       </c>
       <c r="H12" t="n">
-        <v>689852.0477799999</v>
+        <v>559248.6438</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1870,7 +2067,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1896,7 +2093,7 @@
         <v>5544.53</v>
       </c>
       <c r="H13" t="n">
-        <v>999950.4409699999</v>
+        <v>999950.44097</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1907,7 +2104,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1927,13 +2124,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2145.162</v>
+        <v>1795.81</v>
       </c>
       <c r="G14" t="n">
-        <v>218.9</v>
+        <v>219.5</v>
       </c>
       <c r="H14" t="n">
-        <v>469575.9618</v>
+        <v>394180.295</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1944,7 +2141,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1964,13 +2161,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>13218.374</v>
+        <v>11123.162</v>
       </c>
       <c r="G15" t="n">
-        <v>36.73</v>
+        <v>36.44</v>
       </c>
       <c r="H15" t="n">
-        <v>485510.87702</v>
+        <v>405328.02328</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1981,7 +2178,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -2001,13 +2198,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6558.029</v>
+        <v>5029.462</v>
       </c>
       <c r="G16" t="n">
-        <v>90.18000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="H16" t="n">
-        <v>591403.0552200001</v>
+        <v>454562.77556</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2018,7 +2215,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -2055,7 +2252,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -2075,13 +2272,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2476.375</v>
+        <v>2161.085</v>
       </c>
       <c r="G18" t="n">
-        <v>47.65</v>
+        <v>47.66</v>
       </c>
       <c r="H18" t="n">
-        <v>117999.26875</v>
+        <v>102997.3111</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2092,7 +2289,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -2129,7 +2326,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -2166,7 +2363,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -2203,7 +2400,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -2223,13 +2420,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.045</v>
+        <v>5.224</v>
       </c>
       <c r="G22" t="n">
-        <v>1543.71</v>
+        <v>1542.55</v>
       </c>
       <c r="H22" t="n">
-        <v>3156.88695</v>
+        <v>8058.2812</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2240,7 +2437,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -2269,6 +2466,117 @@
         <v>160966.8244</v>
       </c>
       <c r="I23" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HDFC LIQUID FUND - DIRECT PLAN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>INF179KB1HP9</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026.09.01</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>337.8262900552436</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5544.53</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1873088</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HDFC LIQUID FUND - DIRECT PLAN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>INF179KB1HP9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026.09.01</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>81.76220527258397</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5544.53</v>
+      </c>
+      <c r="H25" t="n">
+        <v>453333</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Member B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HDFC LIQUID FUND - DIRECT PLAN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>INF179KB1HP9</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026.09.01</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>13.32577332975022</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5544.53</v>
+      </c>
+      <c r="H26" t="n">
+        <v>73885.14999999999</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
@@ -2285,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2333,7 +2641,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mr. Janak Khandelwal</t>
+          <t>Member C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2343,7 +2651,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>INE092T01019</t>
+          <t>IDFC First Bank</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2351,8 +2659,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>46023</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>1933</v>
@@ -2367,7 +2677,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2377,7 +2687,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INE918I01026</t>
+          <t>Bajaj Finserv</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2385,8 +2695,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>43831</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>20</v>
@@ -2401,7 +2713,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2411,7 +2723,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INE296A01032</t>
+          <t>Bajaj Finance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2419,8 +2731,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>43831</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>40</v>
@@ -2435,7 +2749,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2445,7 +2759,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INE263A01024</t>
+          <t>Bharat Electronics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2453,8 +2767,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>43831</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>150</v>
@@ -2469,7 +2785,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2479,7 +2795,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INE153T01027</t>
+          <t>BLS International</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2487,8 +2803,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>43831</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>400</v>
@@ -2503,7 +2821,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2513,7 +2831,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INE216A01030</t>
+          <t>Britannia Industries</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2521,8 +2839,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>43831</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -2537,7 +2857,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2547,7 +2867,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INE259A01022</t>
+          <t>Colgate-Palmolive (India)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2555,8 +2875,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>43831</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -2571,7 +2893,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2581,7 +2903,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INE758T01015</t>
+          <t>Eternal Limited</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2589,8 +2911,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>43831</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>340</v>
@@ -2605,7 +2929,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2615,7 +2939,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INE040A01034</t>
+          <t>HDFC Bank</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2623,8 +2947,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>43831</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>34</v>
@@ -2639,7 +2965,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2649,7 +2975,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INE795G01014</t>
+          <t>HDFC Life Insurance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2657,8 +2983,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>43831</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>50</v>
@@ -2673,7 +3001,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,7 +3011,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INE031A01017</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2691,8 +3019,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>43831</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F12" t="n">
         <v>200</v>
@@ -2707,7 +3037,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2717,7 +3047,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2725,8 +3055,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>43831</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F13" t="n">
         <v>50</v>
@@ -2741,7 +3073,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2751,7 +3083,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>INE758E01017</t>
+          <t>Jio Financial Services</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2759,8 +3091,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>43831</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F14" t="n">
         <v>152</v>
@@ -2775,7 +3109,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2785,7 +3119,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INE2KCE01013</t>
+          <t>KWIL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2793,8 +3127,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>43831</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>8</v>
@@ -2809,7 +3145,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2819,7 +3155,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INE0FS801015</t>
+          <t>Motherson Sumi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2827,8 +3163,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>43831</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F16" t="n">
         <v>105</v>
@@ -2843,7 +3181,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2853,7 +3191,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>INE663F01032</t>
+          <t>Info Edge (India)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2861,8 +3199,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>43831</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -2877,7 +3217,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2887,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INE589A01014</t>
+          <t>NLC India</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2895,8 +3235,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>43831</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F18" t="n">
         <v>200</v>
@@ -2911,7 +3253,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2921,7 +3263,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INE160A01022</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2929,8 +3271,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>43831</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>1000</v>
@@ -2945,7 +3289,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2955,7 +3299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INE891D01026</t>
+          <t>Redington</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2963,8 +3307,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>43831</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F20" t="n">
         <v>200</v>
@@ -2979,7 +3325,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2989,7 +3335,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>INE062A01020</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2997,8 +3343,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>43831</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F21" t="n">
         <v>10</v>
@@ -3013,7 +3361,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3023,7 +3371,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INE040H01021</t>
+          <t>Suzlon Energy</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3031,8 +3379,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>43831</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F22" t="n">
         <v>1000</v>
@@ -3047,7 +3397,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3057,7 +3407,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INE245A01021</t>
+          <t>Tata Power</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3065,8 +3415,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>43831</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F23" t="n">
         <v>100</v>
@@ -3081,7 +3433,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3091,7 +3443,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INE1TAE01010</t>
+          <t>Tata Motors CV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3099,8 +3451,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>43831</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>25</v>
@@ -3115,7 +3469,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3125,7 +3479,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INE155A01022</t>
+          <t>Tata Motors PV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3133,8 +3487,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>43831</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>25</v>
@@ -3149,7 +3505,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3159,7 +3515,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INE1CDF01017</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3167,8 +3523,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>43831</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F26" t="n">
         <v>100</v>
@@ -3183,7 +3541,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,7 +3551,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INE205A01025</t>
+          <t>Vedanta</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3201,8 +3559,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>43831</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>100</v>
@@ -3217,7 +3577,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3227,7 +3587,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INE694L01019</t>
+          <t>Vedanta Power</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3235,8 +3595,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>43831</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F28" t="n">
         <v>100</v>
@@ -3251,7 +3613,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3261,7 +3623,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INE1CLE01013</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3269,8 +3631,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>43831</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F29" t="n">
         <v>100</v>
@@ -3285,7 +3649,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3295,7 +3659,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INE704J01044</t>
+          <t>VOGL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3303,8 +3667,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>43831</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>100</v>
@@ -3319,7 +3685,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3329,7 +3695,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INE192B01031</t>
+          <t>Welspun Living</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3337,8 +3703,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>43831</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>100</v>
@@ -3353,7 +3721,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3363,7 +3731,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INE914E01040</t>
+          <t>Alankit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3371,8 +3739,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>43831</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F32" t="n">
         <v>3358</v>
@@ -3387,7 +3757,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3397,7 +3767,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INE397D01024</t>
+          <t>Bharti Airtel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3405,8 +3775,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>43831</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -3421,7 +3793,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mr. SATYANARAYAN SHARMA</t>
+          <t>Member D</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3431,7 +3803,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INE758E01017</t>
+          <t>Jio Financial Services</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3439,8 +3811,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>43831</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F34" t="n">
         <v>500</v>
@@ -3455,7 +3829,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mr. SATYANARAYAN SHARMA</t>
+          <t>Member D</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3465,7 +3839,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IN0020230093</t>
+          <t>Sovereign Gold Bond Sep 2031 II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3473,8 +3847,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>43831</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F35" t="n">
         <v>84</v>
@@ -3489,7 +3865,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mrs. KAVITA KHANDELWAL</t>
+          <t>Member A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3499,7 +3875,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IN0020200427</t>
+          <t>Sovereign Gold Bond Mar 2029 XII</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3507,8 +3883,10 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>43831</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
       </c>
       <c r="F36" t="n">
         <v>2</v>
@@ -3523,7 +3901,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mr. RAJESH KUMAR</t>
+          <t>Member B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3533,7 +3911,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INF204KB17I5</t>
+          <t>Nippon India ETF Gold BeES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3541,195 +3919,19 @@
           <t>NSE</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>46252</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>1108</v>
+        <v>775</v>
       </c>
       <c r="G37" t="n">
-        <v>125.14</v>
+        <v>126.61</v>
       </c>
       <c r="H37" t="n">
-        <v>138655.12</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ITBEES</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>INF204KB15V2</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NSE</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>46313</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G38" t="n">
-        <v>34.05</v>
-      </c>
-      <c r="H38" t="n">
-        <v>34050</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Saving Bank Balance</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Rate of Interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ABC2663</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>487301.81</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ABC9613</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>112808.59</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ABC0470</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3561.19</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ABC7784</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>74252.14999999999</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ABC5922</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mr. RAJESH KUMAR</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SNS123</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Mr. SATYANARAYAN SHARMA</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>83532</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.5</v>
+        <v>98122.75</v>
       </c>
     </row>
   </sheetData>
